--- a/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T14:33:31+00:00</t>
+    <t>2024-10-30T15:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T15:48:47+00:00</t>
+    <t>2024-11-17T20:47:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:47:41+00:00</t>
+    <t>2024-11-17T21:11:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:11:32+00:00</t>
+    <t>2024-11-17T21:35:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:35:06+00:00</t>
+    <t>2024-11-27T13:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-27T13:18:58+00:00</t>
+    <t>2024-12-15T14:03:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-15T14:03:14+00:00</t>
+    <t>2024-12-19T08:32:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-19T08:32:44+00:00</t>
+    <t>2025-01-08T14:32:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T14:32:12+00:00</t>
+    <t>2025-01-24T13:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T13:05:30+00:00</t>
+    <t>2025-01-24T15:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T15:13:16+00:00</t>
+    <t>2025-01-27T12:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T09:10:20+00:00</t>
+    <t>2026-03-01T19:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:31:53+00:00</t>
+    <t>2026-07-17T05:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
